--- a/outputs/module1_property_tax.xlsx
+++ b/outputs/module1_property_tax.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V2"/>
+  <dimension ref="A1:X2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -445,100 +445,110 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>School District</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Homes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Average Sale Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Assessment Ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>County Millage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fire EMS Millage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>School Millage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Municipal Millage</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Other Levies</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Applicable Municipal Millage</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>State Sales Tax</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>County Sales Tax</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>City/Local Sales Tax</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Combined Sales Tax</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tax Foundation 2024 Effective Rate</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>District Capacity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PILOT Annual Payment</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Tax District Scenario</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Property Tax Source URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Assessment Ratio Source URL</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>PILOT Source URL</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
@@ -555,58 +565,66 @@
           <t>Kansas</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wichita</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>150</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>223000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.115</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>27.567</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>16.754</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>51.402</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>32.34</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.065</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.01</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.075</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.0118</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Unincorporated Sedgwick Fire Dist 1</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Working Sedgwick example; verify all levy inputs against primary sources before final submission.</t>
         </is>
@@ -623,7 +641,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA2"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -639,125 +657,135 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>School District</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>Homes</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Average Sale Price</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Assessment Ratio</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>County Millage</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Fire EMS Millage</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>School Millage</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Municipal Millage</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Other Levies</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Applicable Municipal Millage</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>State Sales Tax</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>County Sales Tax</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>City/Local Sales Tax</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Combined Sales Tax</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>Tax Foundation 2024 Effective Rate</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>District Capacity</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>PILOT Annual Payment</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>Tax District Scenario</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>Property Tax Source URL</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>Assessment Ratio Source URL</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>PILOT Source URL</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>Notes</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>Gross Market Value</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>Gross Assessed Value</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>Total Applicable Millage</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>Gross Annual Property Tax</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>Gross Tax Per Home</t>
         </is>
@@ -774,75 +802,83 @@
           <t>Kansas</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Wichita</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>150</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>223000</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
         <v>0.115</v>
       </c>
-      <c r="F2" t="n">
+      <c r="G2" t="n">
         <v>27.567</v>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>16.754</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>51.402</v>
       </c>
-      <c r="I2" t="n">
+      <c r="J2" t="n">
         <v>32.34</v>
-      </c>
-      <c r="J2" t="n">
-        <v>0</v>
       </c>
       <c r="K2" t="n">
         <v>0</v>
       </c>
       <c r="L2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" t="n">
         <v>0.065</v>
       </c>
-      <c r="M2" t="n">
+      <c r="N2" t="n">
         <v>0.01</v>
       </c>
-      <c r="N2" t="n">
+      <c r="O2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
+      <c r="P2" t="n">
         <v>0.075</v>
       </c>
-      <c r="P2" t="n">
+      <c r="Q2" t="n">
         <v>0.0118</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr">
+      <c r="R2" t="n">
+        <v>60000</v>
+      </c>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr">
         <is>
           <t>Unincorporated Sedgwick Fire Dist 1</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr">
         <is>
           <t>Working Sedgwick example; verify all levy inputs against primary sources before final submission.</t>
         </is>
       </c>
-      <c r="W2" t="n">
+      <c r="Y2" t="n">
         <v>33450000</v>
       </c>
-      <c r="X2" t="n">
+      <c r="Z2" t="n">
         <v>3846750</v>
       </c>
-      <c r="Y2" t="n">
+      <c r="AA2" t="n">
         <v>95.723</v>
       </c>
-      <c r="Z2" t="n">
-        <v>368222.45025</v>
-      </c>
-      <c r="AA2" t="n">
+      <c r="AB2" t="n">
+        <v>368222.45025</v>
+      </c>
+      <c r="AC2" t="n">
         <v>2454.816335</v>
       </c>
     </row>
